--- a/bonos_flujos.xlsx
+++ b/bonos_flujos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29324"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{530FE1C7-323D-46BF-AAC2-1FC0867BA4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D7680DF-6F07-4314-9A8B-1430D41688A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
-    <t>Bono YPF</t>
+    <t>PAE 2029 7,00%</t>
   </si>
   <si>
     <t>ACT/365</t>
@@ -48,13 +48,13 @@
     <t>30/360</t>
   </si>
   <si>
-    <t>Bono Arcor</t>
+    <t>VISTA 2027 6,5%</t>
   </si>
   <si>
-    <t>Bono PAE</t>
+    <t>YPF 2028 6,5%</t>
   </si>
   <si>
-    <t>PAE 2029 7,00%</t>
+    <t>GD30</t>
   </si>
 </sst>
 </file>
@@ -73,18 +73,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -99,13 +93,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" customWidth="1"/>
@@ -453,35 +446,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="5" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5">
+      <c r="C1">
         <v>2</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="D1" s="1"/>
       <c r="J1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1">
-        <v>45672</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="C2">
-        <v>2.5</v>
-      </c>
-      <c r="E2">
-        <f>+C2+D2</f>
-        <v>2.5</v>
-      </c>
+        <v>45562</v>
+      </c>
+      <c r="B2" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" t="s">
         <v>2</v>
@@ -489,21 +475,19 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1">
-        <v>45853</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.05</v>
+        <v>45743</v>
+      </c>
+      <c r="B3" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E12" si="0">+C3+D3</f>
-        <v>2.5</v>
-      </c>
-      <c r="G3" s="1">
-        <v>45916</v>
-      </c>
+        <f>+C3+D3</f>
+        <v>3.47</v>
+      </c>
+      <c r="G3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" t="s">
         <v>3</v>
@@ -511,21 +495,17 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1">
-        <v>46037</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.05</v>
+        <v>45927</v>
+      </c>
+      <c r="B4" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C4">
-        <v>2.5</v>
+        <v>3.53</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="G4">
-        <f>+G3-A3</f>
-        <v>63</v>
+        <f>+C4+D4</f>
+        <v>3.53</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
@@ -535,144 +515,132 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1">
-        <v>46218</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.05</v>
+        <v>46108</v>
+      </c>
+      <c r="B5" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
+        <f>+C5+D5</f>
+        <v>3.47</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1">
-        <v>46402</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.05</v>
+        <v>46292</v>
+      </c>
+      <c r="B6" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>3.53</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="G6">
-        <f>100*B3</f>
-        <v>5</v>
+        <f>+C6+D6</f>
+        <v>3.53</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1">
-        <v>46583</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.05</v>
+        <v>46473</v>
+      </c>
+      <c r="B7" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="G7">
-        <f>+G6/365</f>
-        <v>1.3698630136986301E-2</v>
+        <f>+C7+D7</f>
+        <v>3.47</v>
       </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1">
-        <v>46767</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.05</v>
+        <v>46657</v>
+      </c>
+      <c r="B8" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3.53</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="G8">
-        <f>+G7*G4</f>
-        <v>0.86301369863013688</v>
+        <f>+C8+D8</f>
+        <v>3.53</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1">
-        <v>46949</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0.05</v>
+        <v>46839</v>
+      </c>
+      <c r="B9" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
+        <f>+C9+D9</f>
+        <v>3.47</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1">
-        <v>47133</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0.05</v>
+        <v>47023</v>
+      </c>
+      <c r="B10" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>3.53</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
+        <f>+C10+D10</f>
+        <v>3.53</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1">
-        <v>47314</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.05</v>
+        <v>47204</v>
+      </c>
+      <c r="B11" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C11">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
+        <f>+C11+D11</f>
+        <v>3.47</v>
       </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1">
-        <v>47498</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0.05</v>
+        <v>47388</v>
+      </c>
+      <c r="B12" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C12">
-        <v>2.5</v>
+        <v>3.53</v>
       </c>
       <c r="D12">
         <v>100</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
-        <v>102.5</v>
+        <f>+C12+D12</f>
+        <v>103.53</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -681,1092 +649,839 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1">
-        <v>43816</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <f>+C14+D14</f>
-        <v>2</v>
+        <v>45357</v>
+      </c>
+      <c r="B14" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1">
-        <v>43907</v>
-      </c>
-      <c r="B15" s="4">
-        <v>0.04</v>
+        <v>45541</v>
+      </c>
+      <c r="B15" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="E15">
-        <f t="shared" ref="E15:E77" si="1">+C15+D15</f>
-        <v>2</v>
+        <f t="shared" ref="E15:E20" si="0">+C15+D15</f>
+        <v>3.28</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1">
-        <v>43999</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0.04</v>
+        <v>45722</v>
+      </c>
+      <c r="B16" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3.22</v>
       </c>
       <c r="E16">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3.22</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1">
-        <v>44091</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0.04</v>
+        <v>45906</v>
+      </c>
+      <c r="B17" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="E17">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3.28</v>
       </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1">
-        <v>44182</v>
-      </c>
-      <c r="B18" s="4">
-        <v>0.04</v>
+        <v>46087</v>
+      </c>
+      <c r="B18" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3.22</v>
       </c>
       <c r="E18">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3.22</v>
       </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1">
-        <v>44272</v>
-      </c>
-      <c r="B19" s="4">
-        <v>0.04</v>
+        <v>46271</v>
+      </c>
+      <c r="B19" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="E19">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3.28</v>
       </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1">
-        <v>44364</v>
-      </c>
-      <c r="B20" s="4">
-        <v>0.04</v>
+        <v>46452</v>
+      </c>
+      <c r="B20" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3.22</v>
+      </c>
+      <c r="D20">
+        <v>100</v>
       </c>
       <c r="E20">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>103.22</v>
       </c>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="1">
-        <v>44456</v>
-      </c>
-      <c r="B21" s="4">
-        <v>0.04</v>
+      <c r="A21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1">
-        <v>44547</v>
-      </c>
-      <c r="B22" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <v>45575</v>
+      </c>
+      <c r="B22" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1">
-        <v>44637</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0.04</v>
+        <v>45848</v>
+      </c>
+      <c r="B23" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E23">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" ref="E23:E36" si="1">+C23+D23</f>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1">
-        <v>44729</v>
-      </c>
-      <c r="B24" s="4">
-        <v>0.04</v>
+        <v>45940</v>
+      </c>
+      <c r="B24" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="E24">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1">
-        <v>44821</v>
-      </c>
-      <c r="B25" s="4">
-        <v>0.04</v>
+        <v>46032</v>
+      </c>
+      <c r="B25" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>10</v>
+        <v>1.64</v>
       </c>
       <c r="E25">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1.64</v>
       </c>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1">
-        <v>44912</v>
-      </c>
-      <c r="B26" s="4">
-        <v>0.04</v>
+        <v>46122</v>
+      </c>
+      <c r="B26" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E26">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1">
-        <v>45002</v>
-      </c>
-      <c r="B27" s="4">
-        <v>0.04</v>
+        <v>46213</v>
+      </c>
+      <c r="B27" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="E27">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1">
-        <v>45094</v>
-      </c>
-      <c r="B28" s="4">
-        <v>0.04</v>
+        <v>46305</v>
+      </c>
+      <c r="B28" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>10</v>
+        <v>1.64</v>
       </c>
       <c r="E28">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1.64</v>
       </c>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1">
-        <v>45186</v>
-      </c>
-      <c r="B29" s="4">
-        <v>0.04</v>
+        <v>46397</v>
+      </c>
+      <c r="B29" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="E29">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="I29" s="1"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1">
-        <v>45277</v>
-      </c>
-      <c r="B30" s="4">
-        <v>0.04</v>
+        <v>46487</v>
+      </c>
+      <c r="B30" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E30">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1">
-        <v>45368</v>
-      </c>
-      <c r="B31" s="4">
-        <v>0.04</v>
+        <v>46578</v>
+      </c>
+      <c r="B31" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="E31">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1.62</v>
       </c>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1">
-        <v>45460</v>
-      </c>
-      <c r="B32" s="4">
-        <v>0.04</v>
+        <v>46670</v>
+      </c>
+      <c r="B32" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="E32">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1">
-        <v>45552</v>
-      </c>
-      <c r="B33" s="4">
-        <v>0.04</v>
+        <v>46762</v>
+      </c>
+      <c r="B33" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="E33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
-        <v>45643</v>
-      </c>
-      <c r="B34" s="4">
-        <v>0.04</v>
+        <v>46853</v>
+      </c>
+      <c r="B34" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="E34">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1.62</v>
       </c>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="1">
-        <v>45733</v>
-      </c>
-      <c r="B35" s="4">
-        <v>0.04</v>
+        <v>46944</v>
+      </c>
+      <c r="B35" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="E35">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="1">
-        <v>45825</v>
-      </c>
-      <c r="B36" s="4">
-        <v>0.04</v>
+        <v>47036</v>
+      </c>
+      <c r="B36" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1.64</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
       </c>
       <c r="E36">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>101.64</v>
       </c>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="1">
-        <v>45917</v>
-      </c>
-      <c r="B37" s="4">
-        <v>0.04</v>
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
-      <c r="D37">
-        <v>10</v>
-      </c>
-      <c r="E37">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="1">
-        <v>46008</v>
-      </c>
-      <c r="B38" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="E38">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <v>43930</v>
       </c>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="1">
-        <v>46098</v>
-      </c>
-      <c r="B39" s="4">
-        <v>0.04</v>
+        <v>44386</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1.25E-3</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>0.16</v>
       </c>
       <c r="E39">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" ref="E39:E57" si="2">+C39+D39</f>
+        <v>0.16</v>
       </c>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1">
-        <v>46190</v>
-      </c>
-      <c r="B40" s="4">
-        <v>0.04</v>
+        <v>44570</v>
+      </c>
+      <c r="B40" s="5">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C40">
-        <v>2</v>
-      </c>
-      <c r="D40">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="E40">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f t="shared" si="2"/>
+        <v>0.25</v>
       </c>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1">
-        <v>46282</v>
-      </c>
-      <c r="B41" s="4">
-        <v>0.04</v>
+        <v>44751</v>
+      </c>
+      <c r="B41" s="5">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="E41">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>0.25</v>
       </c>
       <c r="I41" s="1"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="1">
-        <v>46373</v>
-      </c>
-      <c r="B42" s="4">
-        <v>0.04</v>
+        <v>44935</v>
+      </c>
+      <c r="B42" s="5">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="E42">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>0.25</v>
       </c>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="1">
-        <v>46463</v>
-      </c>
-      <c r="B43" s="4">
-        <v>0.04</v>
+        <v>45116</v>
+      </c>
+      <c r="B43" s="5">
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="D43">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="E43">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f t="shared" si="2"/>
+        <v>0.25</v>
       </c>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1">
-        <v>46555</v>
-      </c>
-      <c r="B44" s="4">
-        <v>0.04</v>
+        <v>45300</v>
+      </c>
+      <c r="B44" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>0.38</v>
       </c>
       <c r="E44">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>0.38</v>
       </c>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1">
-        <v>46647</v>
-      </c>
-      <c r="B45" s="4">
-        <v>0.04</v>
+        <v>45482</v>
+      </c>
+      <c r="B45" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>0.38</v>
+      </c>
+      <c r="D45">
+        <v>4</v>
       </c>
       <c r="E45">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4.38</v>
       </c>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1">
-        <v>46738</v>
-      </c>
-      <c r="B46" s="4">
-        <v>0.04</v>
+        <v>45666</v>
+      </c>
+      <c r="B46" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>0.36</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f t="shared" si="2"/>
+        <v>8.36</v>
       </c>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1">
-        <v>46829</v>
-      </c>
-      <c r="B47" s="4">
-        <v>0.04</v>
+        <v>45847</v>
+      </c>
+      <c r="B47" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0.33</v>
+      </c>
+      <c r="D47">
+        <v>8</v>
       </c>
       <c r="E47">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>8.33</v>
       </c>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1">
-        <v>46921</v>
-      </c>
-      <c r="B48" s="4">
-        <v>0.04</v>
+        <v>46031</v>
+      </c>
+      <c r="B48" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>0.3</v>
+      </c>
+      <c r="D48">
+        <v>8</v>
       </c>
       <c r="E48">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="1">
-        <v>47013</v>
-      </c>
-      <c r="B49" s="4">
-        <v>0.04</v>
+        <v>46212</v>
+      </c>
+      <c r="B49" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>0.27</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f t="shared" si="2"/>
+        <v>8.27</v>
       </c>
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="1">
-        <v>47104</v>
-      </c>
-      <c r="B50" s="4">
-        <v>0.04</v>
+        <v>46396</v>
+      </c>
+      <c r="B50" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>0.24</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
       </c>
       <c r="E50">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>8.24</v>
       </c>
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="1">
-        <v>47194</v>
-      </c>
-      <c r="B51" s="4">
-        <v>0.04</v>
+        <v>46577</v>
+      </c>
+      <c r="B51" s="5">
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>0.21</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
       </c>
       <c r="E51">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>8.2100000000000009</v>
       </c>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="1">
-        <v>47286</v>
-      </c>
-      <c r="B52" s="4">
-        <v>0.04</v>
+        <v>46761</v>
+      </c>
+      <c r="B52" s="5">
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>0.42</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E52">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f t="shared" si="2"/>
+        <v>8.42</v>
       </c>
       <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" t="s">
-        <v>4</v>
+      <c r="A53" s="1">
+        <v>46943</v>
+      </c>
+      <c r="B53" s="5">
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>0.35</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="2"/>
+        <v>8.35</v>
       </c>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1">
-        <v>45794</v>
-      </c>
-      <c r="B54" s="4">
-        <v>0.1</v>
+        <v>47127</v>
+      </c>
+      <c r="B54" s="5">
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D54">
+        <v>8</v>
       </c>
       <c r="E54">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>8.2799999999999994</v>
       </c>
       <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="1">
-        <v>45978</v>
-      </c>
-      <c r="B55" s="4">
-        <v>0.1</v>
+        <v>47308</v>
+      </c>
+      <c r="B55" s="5">
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>0.21</v>
+      </c>
+      <c r="D55">
+        <v>8</v>
       </c>
       <c r="E55">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>8.2100000000000009</v>
       </c>
       <c r="I55" s="1"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="1">
-        <v>46159</v>
-      </c>
-      <c r="B56" s="4">
-        <v>0.1</v>
+        <v>47492</v>
+      </c>
+      <c r="B56" s="5">
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D56">
+        <v>8</v>
       </c>
       <c r="E56">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>8.14</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1">
-        <v>46343</v>
-      </c>
-      <c r="B57" s="4">
-        <v>0.1</v>
+        <v>47673</v>
+      </c>
+      <c r="B57" s="5">
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
       </c>
       <c r="E57">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>8.07</v>
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="1">
-        <v>46524</v>
-      </c>
-      <c r="B58" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C58">
-        <v>5</v>
-      </c>
-      <c r="E58">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="A58" s="1"/>
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="1">
-        <v>46708</v>
-      </c>
-      <c r="B59" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C59">
-        <v>5</v>
-      </c>
-      <c r="E59">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="4"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="1">
-        <v>46890</v>
-      </c>
-      <c r="B60" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C60">
-        <v>5</v>
-      </c>
-      <c r="E60">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="4"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="1">
-        <v>47074</v>
-      </c>
-      <c r="B61" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C61">
-        <v>5</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="4"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="1">
-        <v>47255</v>
-      </c>
-      <c r="B62" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C62">
-        <v>5</v>
-      </c>
-      <c r="E62">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="4"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="1">
-        <v>47439</v>
-      </c>
-      <c r="B63" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C63">
-        <v>5</v>
-      </c>
-      <c r="E63">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="4"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="1">
-        <v>47620</v>
-      </c>
-      <c r="B64" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C64">
-        <v>5</v>
-      </c>
-      <c r="E64">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="1">
-        <v>47804</v>
-      </c>
-      <c r="B65" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C65">
-        <v>5</v>
-      </c>
-      <c r="E65">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="1">
-        <v>47985</v>
-      </c>
-      <c r="B66" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="C66">
-        <v>5</v>
-      </c>
-      <c r="D66">
-        <v>100</v>
-      </c>
-      <c r="E66">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>2</v>
-      </c>
-      <c r="D67" s="1">
-        <v>45562</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="1">
-        <v>45743</v>
-      </c>
-      <c r="B68" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C68">
-        <v>3.47</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="1"/>
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="1">
-        <v>45927</v>
-      </c>
-      <c r="B69" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C69">
-        <v>3.53</v>
-      </c>
-      <c r="E69">
-        <f t="shared" si="1"/>
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="1">
-        <v>46108</v>
-      </c>
-      <c r="B70" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C70">
-        <v>3.47</v>
-      </c>
-      <c r="E70">
-        <f t="shared" si="1"/>
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="1">
-        <v>46292</v>
-      </c>
-      <c r="B71" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C71">
-        <v>3.53</v>
-      </c>
-      <c r="E71">
-        <f t="shared" si="1"/>
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="1">
-        <v>46473</v>
-      </c>
-      <c r="B72" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C72">
-        <v>3.47</v>
-      </c>
-      <c r="E72">
-        <f t="shared" si="1"/>
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="1">
-        <v>46657</v>
-      </c>
-      <c r="B73" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C73">
-        <v>3.53</v>
-      </c>
-      <c r="E73">
-        <f t="shared" si="1"/>
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="1">
-        <v>46839</v>
-      </c>
-      <c r="B74" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C74">
-        <v>3.47</v>
-      </c>
-      <c r="E74">
-        <f t="shared" si="1"/>
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="1">
-        <v>47023</v>
-      </c>
-      <c r="B75" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C75">
-        <v>3.53</v>
-      </c>
-      <c r="E75">
-        <f t="shared" si="1"/>
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="1">
-        <v>47204</v>
-      </c>
-      <c r="B76" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C76">
-        <v>3.47</v>
-      </c>
-      <c r="E76">
-        <f t="shared" si="1"/>
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="1">
-        <v>47388</v>
-      </c>
-      <c r="B77" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C77">
-        <v>3.53</v>
-      </c>
-      <c r="D77">
-        <v>100</v>
-      </c>
-      <c r="E77">
-        <f t="shared" si="1"/>
-        <v>103.53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="1"/>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="1"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="1"/>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="1"/>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="1"/>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="1"/>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="1"/>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="1"/>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="1"/>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="1"/>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="1"/>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="1"/>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="1"/>
+      <c r="A64" s="1"/>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1"/>
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1"/>
+      <c r="B66" s="4"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="1"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="1"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="1"/>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="1"/>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="1"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="1"/>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="1"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1"/>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="1"/>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1"/>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="1"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B53 B13 B67" xr:uid="{BD1BD003-9C46-4FBD-99EA-FC0DAEFD6ABE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B13 B21 B37" xr:uid="{BD1BD003-9C46-4FBD-99EA-FC0DAEFD6ABE}">
       <formula1>$J$1:$J$4</formula1>
     </dataValidation>
   </dataValidations>
